--- a/output/pdf_financials_xlsx/SXP.xlsx
+++ b/output/pdf_financials_xlsx/SXP.xlsx
@@ -4680,25 +4680,25 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-0.05099</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.021072</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.836511</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.635355</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.347859</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.875692</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.175893</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>0</v>
@@ -13389,7 +13389,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>-0.05099</v>
       </c>

--- a/output/pdf_financials_xlsx/SXP.xlsx
+++ b/output/pdf_financials_xlsx/SXP.xlsx
@@ -2014,43 +2014,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.506205</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.364079</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.533917</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.964947</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.70619</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.308941</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.222889</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.035999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.364662</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.928539</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.066</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.794</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="35">
@@ -2106,43 +2106,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.506205</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.364079</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.533917</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.964947</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.70619</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.308941</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.222889</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.035999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>6.364662</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.928539</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.066</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.794</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="37">
@@ -2658,43 +2658,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.028238</v>
+        <v>0.522033</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.922643</v>
+        <v>0.5585639999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.187497</v>
+        <v>0.65358</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.085374</v>
+        <v>1.120427</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.257606</v>
+        <v>1.551416</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.214852</v>
+        <v>2.905911</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.633041</v>
+        <v>3.410152</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.703813</v>
+        <v>1.667814</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7.732708</v>
+        <v>1.368046</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.495688</v>
+        <v>2.567149</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.43</v>
+        <v>4.364</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>15.341</v>
+        <v>13.547</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.433</v>
+        <v>4.343</v>
       </c>
     </row>
     <row r="49">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/SXP.xlsx
+++ b/output/pdf_financials_xlsx/SXP.xlsx
@@ -1792,28 +1792,28 @@
         <v>1.682702</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2.088659</v>
+        <v>6.383683</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2.193257</v>
+        <v>11.727132</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3.355591</v>
+        <v>13.888091</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.381104</v>
+        <v>13.52431</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>3.761866</v>
+        <v>14.089849</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>6.663</v>
+        <v>18.837</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>6.917</v>
+        <v>19.656</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>6.903</v>
+        <v>18.704</v>
       </c>
     </row>
     <row r="29">
@@ -1838,28 +1838,28 @@
         <v>18.729517</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.370058</v>
+        <v>5.665082</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>12.33859</v>
+        <v>21.872465</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>13.63989</v>
+        <v>24.17239</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>24.434258</v>
+        <v>34.577464</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>41.854543</v>
+        <v>52.182526</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>29.999</v>
+        <v>42.173</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.029</v>
+        <v>10.71</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>18.268</v>
+        <v>30.069</v>
       </c>
     </row>
     <row r="30">
@@ -1884,28 +1884,28 @@
         <v>10.45916593042496</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.7022795130466732</v>
+        <v>2.903870513751588</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>6.437441743364107</v>
+        <v>11.41157289619563</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>6.666468463075772</v>
+        <v>11.81420639111959</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.79108939596228</v>
+        <v>15.27071151944402</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>15.36131003122738</v>
+        <v>19.15185073454472</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>9.927296673913835</v>
+        <v>13.95592795189734</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-0.7219741313359546</v>
+        <v>3.810913231448041</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>6.648227673047528</v>
+        <v>10.94293616711551</v>
       </c>
     </row>
     <row r="31">
@@ -5055,43 +5055,43 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>6.1639</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>6.1639</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>6.211107</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.916581</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.682702</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>6.383683</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>11.727132</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>13.888091</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>13.52431</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>14.089849</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>18.837</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>19.656</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>18.704</v>
       </c>
     </row>
     <row r="101">
@@ -5622,28 +5622,28 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>4.205836</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.424023</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.052516</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.543259</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>2.335</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>1.055</v>
       </c>
     </row>
     <row r="113">
@@ -19228,7 +19228,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -19305,7 +19309,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -19384,7 +19392,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -21451,7 +21459,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -23263,7 +23275,11 @@
           <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -23338,7 +23354,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -23419,7 +23439,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -24438,7 +24458,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -24515,7 +24539,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -24594,7 +24622,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -26889,7 +26917,11 @@
           <t>Proceeds from the disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -27122,7 +27154,11 @@
           <t>Depreciation of right-of-use assets 4</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -31477,7 +31513,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E318" s="5" t="n">
@@ -32911,7 +32947,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -32988,7 +33028,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -33067,7 +33111,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -34876,7 +34920,11 @@
           <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -34951,7 +34999,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -35032,7 +35084,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -35907,7 +35959,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -35984,7 +36040,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -36063,7 +36123,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -36940,7 +37000,11 @@
           <t>Depreciation of right-of-use assets 4</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -37748,7 +37812,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -38722,7 +38786,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -39698,7 +39762,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -40757,7 +40821,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E434" s="5" t="n">

--- a/output/pdf_financials_xlsx/SXP.xlsx
+++ b/output/pdf_financials_xlsx/SXP.xlsx
@@ -1175,7 +1175,7 @@
         <v>-2.797</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>0.657</v>
       </c>
     </row>
     <row r="18">
@@ -1364,10 +1364,8 @@
       <c r="M20" s="3" t="n">
         <v>-11.743</v>
       </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N20" s="3" t="n">
+        <v>12.022</v>
       </c>
     </row>
     <row r="21">
@@ -1505,7 +1503,7 @@
         <v>-11.743</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>11.365</v>
+        <v>12.022</v>
       </c>
     </row>
     <row r="24">
@@ -1951,7 +1949,7 @@
         <v>-31.26536999776436</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>5.78090629124505</v>
       </c>
     </row>
     <row r="32">
@@ -1997,7 +1995,7 @@
         <v>-4.178483107086306</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>4.13603610160856</v>
+        <v>4.375136472814615</v>
       </c>
     </row>
     <row r="33">
@@ -2290,43 +2288,43 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.383854</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>1.105001</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.943528</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.701423</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1.411004</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>872153</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>642116</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>2.509048</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.842151</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.57644</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.805</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.578</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="41">
@@ -2336,43 +2334,43 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>17.375214</v>
+        <v>17.759068</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>18.560419</v>
+        <v>19.66542</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>21.358826</v>
+        <v>22.302354</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>21.237321</v>
+        <v>21.938744</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>25.97701</v>
+        <v>27.388014</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>26.51824</v>
+        <v>872179.51824</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>22.340239</v>
+        <v>642138.340239</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>26.855191</v>
+        <v>29.364239</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>32.982719</v>
+        <v>33.82487</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>39.334457</v>
+        <v>39.910897</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>33.64</v>
+        <v>34.445</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>32.27</v>
+        <v>32.848</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>34.546</v>
+        <v>35.655</v>
       </c>
     </row>
     <row r="42">
@@ -2658,43 +2656,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.522033</v>
+        <v>0.138179</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.5585639999999999</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.65358</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.120427</v>
+        <v>0.419004</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.551416</v>
+        <v>0.140412</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.905911</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.410152</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.667814</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.368046</v>
+        <v>0.525895</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.567149</v>
+        <v>1.990709</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.364</v>
+        <v>3.559</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>13.547</v>
+        <v>12.969</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.343</v>
+        <v>3.234</v>
       </c>
     </row>
     <row r="49">
@@ -3420,43 +3418,43 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>6.578912</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>8.036688</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>8.175682999999999</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>8.833102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>10.033787</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>10945666</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>6967180</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>9.49849</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>11.49485</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>16.288415</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>11.254</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>11.843</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>16.184</v>
       </c>
     </row>
     <row r="65">
@@ -3558,19 +3556,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>7.839367</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>8.382614</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>9.972032</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>9.048705</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>9.961197</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -5045,7 +5043,7 @@
         <v>-11.743</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>11.365</v>
+        <v>12.022</v>
       </c>
     </row>
     <row r="100">
@@ -5067,7 +5065,7 @@
         <v>1.916581</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>1.682702</v>
+        <v>5.395898</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>6.383683</v>
@@ -5208,7 +5206,7 @@
         <v>-0.222221</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.266103</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>0</v>
@@ -5346,7 +5344,7 @@
         <v>-2.138891</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.212729</v>
+        <v>-0.478832</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>-0.158749</v>
@@ -5619,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.903127</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>4.205836</v>
@@ -5797,37 +5795,37 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.238996</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.770446</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.373835</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.343699</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.56528</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.460435</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.550357</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.372074</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.352</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.114</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.083</v>
       </c>
     </row>
     <row r="117">
@@ -6439,7 +6437,7 @@
         <v>-8.529086</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>4.464383</v>
+        <v>8.084624</v>
       </c>
       <c r="G129" s="3" t="n">
         <v>3.379072</v>
@@ -6765,7 +6763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q442"/>
+  <dimension ref="A1:Q451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8689,7 +8687,11 @@
           <t>Lease liabilities 17</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -10516,7 +10518,11 @@
           <t>Lease liabilities 16</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12076,7 +12082,11 @@
           <t>Lease liabilities 15</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -13091,7 +13101,11 @@
           <t>Lease liabilities 4</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -19941,7 +19955,11 @@
           <t>Deferred tax recovery 18</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -20504,10 +20522,8 @@
       <c r="I175" s="5" t="n">
         <v>19.551929</v>
       </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J175" s="5" t="n">
+        <v>16.490766</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -21301,7 +21317,11 @@
           <t>Acquisition of intangible assets 12</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -22986,15 +23006,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I208" s="5" t="n">
+        <v>12.390828</v>
+      </c>
+      <c r="J208" s="5" t="n">
+        <v>-4.79311</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -23300,10 +23316,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I212" s="5" t="n">
+        <v>3.713196</v>
       </c>
       <c r="J212" s="5" t="n">
         <v>4.295024</v>
@@ -23463,10 +23477,8 @@
       <c r="I214" s="5" t="n">
         <v>1.682702</v>
       </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J214" s="5" t="n">
+        <v>2.088659</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -23538,10 +23550,8 @@
       <c r="I215" s="5" t="n">
         <v>0.06862799999999999</v>
       </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J215" s="5" t="n">
+        <v>0.06862799999999999</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -23670,7 +23680,11 @@
           <t>Deferred tax recovery 17</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -23903,7 +23917,11 @@
           <t>Acquisition of intangible assets 11</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -24839,7 +24857,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -24861,10 +24883,8 @@
       <c r="I232" s="5" t="n">
         <v>-0.629423</v>
       </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J232" s="5" t="n">
+        <v>-0.628695</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
@@ -25149,7 +25169,11 @@
           <t>Acquisition of intangible assets 10</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -25639,10 +25663,8 @@
       <c r="I242" s="5" t="n">
         <v>-0.938759</v>
       </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J242" s="5" t="n">
+        <v>-0.43184</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -26112,7 +26134,11 @@
           <t>Deferred income tax expense 16</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -26212,15 +26238,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I250" s="5" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="J250" s="5" t="n">
+        <v>0.101</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -26503,10 +26525,8 @@
       <c r="I254" s="5" t="n">
         <v>-0.222221</v>
       </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J254" s="5" t="n">
+        <v>-0.266103</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -27399,7 +27419,11 @@
           <t>Deferred income tax expense (recovery) 15</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -27657,10 +27681,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I269" s="5" t="n">
+        <v>-0.114786</v>
       </c>
       <c r="J269" s="5" t="n">
         <v>-0.6684330000000001</v>
@@ -27969,10 +27991,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I273" s="5" t="n">
+        <v>-17.930008</v>
       </c>
       <c r="J273" s="5" t="n">
         <v>-11.696509</v>
@@ -28571,7 +28591,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Amortization of property, plant and equipment 8</t>
+          <t>(Gain) loss on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -28581,21 +28601,21 @@
         </is>
       </c>
       <c r="F281" s="5" t="n">
-        <v>3.567177</v>
+        <v>0.005617</v>
       </c>
       <c r="G281" s="5" t="n">
-        <v>4.110569</v>
-      </c>
-      <c r="H281" s="5" t="n">
-        <v>4.519575</v>
+        <v>-0.00674</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I281" s="5" t="n">
-        <v>3.713196</v>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.114533</v>
+      </c>
+      <c r="J281" s="5" t="n">
+        <v>-0.77774</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -28646,7 +28666,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Loss on disposal of property, plant and equipment</t>
+          <t>Goodwill impairment 12</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -28665,16 +28685,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H282" s="5" t="n">
-        <v>0.026766</v>
-      </c>
-      <c r="I282" s="5" t="n">
-        <v>0.114533</v>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J282" s="5" t="n">
+        <v>16.137</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -28801,12 +28823,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Change in employees benefits</t>
+          <t>Variation in provisions 14</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -28815,22 +28837,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F284" s="5" t="n">
-        <v>0.420364</v>
-      </c>
-      <c r="G284" s="5" t="n">
-        <v>-3.478094</v>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H284" s="5" t="n">
-        <v>0.676754</v>
+        <v>-0.008703000000000001</v>
       </c>
       <c r="I284" s="5" t="n">
-        <v>0.0197</v>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.033372</v>
+      </c>
+      <c r="J284" s="5" t="n">
+        <v>0.738309</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -28881,7 +28905,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Variation in provisions 14</t>
+          <t>Change in other long-term liability 5</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -28900,16 +28924,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H285" s="5" t="n">
-        <v>-0.008703000000000001</v>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I285" s="5" t="n">
-        <v>-0.033372</v>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.427</v>
+      </c>
+      <c r="J285" s="5" t="n">
+        <v>-0.427</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -28955,12 +28979,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>Adjustments to consideration paid for previous business</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Variation in income tax payable</t>
+          <t>Adjustments to consideration paid for previous business combinations</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -28969,17 +28993,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F286" s="5" t="n">
-        <v>0.316491</v>
-      </c>
-      <c r="G286" s="5" t="n">
-        <v>-0.386685</v>
-      </c>
-      <c r="H286" s="5" t="n">
-        <v>-1.308132</v>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I286" s="5" t="n">
-        <v>-0.114786</v>
+        <v>0.463533</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -29030,15 +29060,19 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>Adjustments to consideration paid for previous business</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Change in other long term liability 5</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
+          <t>Acquisition of property, plant and equipment 8</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -29060,12 +29094,10 @@
         </is>
       </c>
       <c r="I287" s="5" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.062692</v>
+      </c>
+      <c r="J287" s="5" t="n">
+        <v>-8.216739</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -29111,15 +29143,19 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Adjustments to considerations paid for previous business</t>
+          <t>Adjustments to consideration paid for previous business</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Adjustments to considerations paid for previous business combinations</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
+          <t>Acquisition of intangible assets 11</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -29141,12 +29177,10 @@
         </is>
       </c>
       <c r="I288" s="5" t="n">
-        <v>0.463533</v>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.373835</v>
+      </c>
+      <c r="J288" s="5" t="n">
+        <v>-0.343699</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -29192,17 +29226,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Adjustments to considerations paid for previous business</t>
+          <t>Adjustments to consideration paid for previous business</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Acquisition of property, plant and equipment 8</t>
+          <t>Proceeds from the disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>PurchaseOfPPE</t>
+          <t>SaleOfPPE</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -29220,16 +29254,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H289" s="5" t="n">
-        <v>-1.635186</v>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I289" s="5" t="n">
-        <v>-8.062692</v>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.903127</v>
+      </c>
+      <c r="J289" s="5" t="n">
+        <v>4.205836</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -29275,15 +29309,19 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Adjustments to considerations paid for previous business</t>
+          <t>Adjustments to consideration paid for previous business</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Acquisition of intangibles assets 11</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -29299,16 +29337,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H290" s="5" t="n">
-        <v>-0.770446</v>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I290" s="5" t="n">
-        <v>-0.373835</v>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-24.999875</v>
+      </c>
+      <c r="J290" s="5" t="n">
+        <v>-16.051111</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -29354,12 +29392,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Adjustments to considerations paid for previous business</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Proceeds from sale of property, plant and equipment</t>
+          <t>Increase of secured credit facility</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -29378,16 +29416,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H291" s="5" t="n">
-        <v>0.07598199999999999</v>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I291" s="5" t="n">
-        <v>0.903127</v>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.868344</v>
+      </c>
+      <c r="J291" s="5" t="n">
+        <v>10.994682</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -29433,17 +29471,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Adjustments to considerations paid for previous business</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities</t>
+          <t>Dividends paid 19</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>CashDividendsPaid</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -29462,15 +29500,13 @@
         </is>
       </c>
       <c r="H292" s="5" t="n">
-        <v>-14.313085</v>
+        <v>-6.307029</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>-24.999875</v>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.844961</v>
+      </c>
+      <c r="J292" s="5" t="n">
+        <v>-7.370796</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -29521,10 +29557,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Increase (repayment) of secured credit facility</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
+          <t>Net cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -29540,16 +29580,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H293" s="5" t="n">
-        <v>-1.848735</v>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I293" s="5" t="n">
-        <v>15.868344</v>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.084624</v>
+      </c>
+      <c r="J293" s="5" t="n">
+        <v>3.379072</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -29600,39 +29640,31 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Dividends paid 19</t>
+          <t>Net change in cash</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>CashDividendsPaid</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n">
+        <v>-3.561413</v>
+      </c>
+      <c r="F294" s="5" t="n">
+        <v>-1.143542</v>
+      </c>
+      <c r="G294" s="5" t="n">
+        <v>2.922898</v>
       </c>
       <c r="H294" s="5" t="n">
-        <v>-6.307029</v>
+        <v>-1.515611</v>
       </c>
       <c r="I294" s="5" t="n">
-        <v>-6.844961</v>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.983563</v>
+      </c>
+      <c r="J294" s="5" t="n">
+        <v>-0.735183</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -29683,31 +29715,31 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Net cash flows from (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="n">
+        <v>5.093876</v>
       </c>
       <c r="F295" s="5" t="n">
-        <v>-20.954677</v>
+        <v>1.506205</v>
       </c>
       <c r="G295" s="5" t="n">
-        <v>0.317077</v>
+        <v>0.364079</v>
       </c>
       <c r="H295" s="5" t="n">
-        <v>-8.824703</v>
+        <v>3.533917</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>8.084624</v>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.964947</v>
+      </c>
+      <c r="J295" s="5" t="n">
+        <v>0.70619</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -29758,33 +29790,31 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
+          <t>Cash, ending of period</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E296" s="5" t="n">
-        <v>-3.561413</v>
+        <v>1.506205</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-1.143542</v>
+        <v>0.364079</v>
       </c>
       <c r="G296" s="5" t="n">
-        <v>2.922898</v>
+        <v>3.533917</v>
       </c>
       <c r="H296" s="5" t="n">
-        <v>-1.515611</v>
+        <v>1.964947</v>
       </c>
       <c r="I296" s="5" t="n">
-        <v>-0.983563</v>
-      </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.70619</v>
+      </c>
+      <c r="J296" s="5" t="n">
+        <v>0.308941</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -29830,33 +29860,31 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E297" s="5" t="n">
-        <v>5.093876</v>
+          <t>Amortization of property, plant and equipment 8</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F297" s="5" t="n">
-        <v>1.506205</v>
+        <v>3.567177</v>
       </c>
       <c r="G297" s="5" t="n">
-        <v>0.364079</v>
+        <v>4.110569</v>
       </c>
       <c r="H297" s="5" t="n">
-        <v>3.533917</v>
+        <v>4.519575</v>
       </c>
       <c r="I297" s="5" t="n">
-        <v>1.964947</v>
+        <v>3.713196</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -29907,33 +29935,35 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Cash, ending of period</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E298" s="5" t="n">
-        <v>1.506205</v>
-      </c>
-      <c r="F298" s="5" t="n">
-        <v>0.364079</v>
-      </c>
-      <c r="G298" s="5" t="n">
-        <v>3.533917</v>
+          <t>Loss on disposal of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H298" s="5" t="n">
-        <v>1.964947</v>
+        <v>0.026766</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>0.70619</v>
+        <v>0.114533</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -29989,7 +30019,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Loss (gain) on disposal of property, plant and equipment</t>
+          <t>Change in employees benefits</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -29998,21 +30028,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F299" s="5" t="n">
+        <v>0.420364</v>
       </c>
       <c r="G299" s="5" t="n">
-        <v>-0.00674</v>
+        <v>-3.478094</v>
       </c>
       <c r="H299" s="5" t="n">
-        <v>0.026766</v>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.676754</v>
+      </c>
+      <c r="I299" s="5" t="n">
+        <v>0.0197</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -30063,12 +30089,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 15</t>
+          <t>Variation in income tax payable</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -30078,18 +30104,16 @@
         </is>
       </c>
       <c r="F300" s="5" t="n">
-        <v>-1.58568</v>
+        <v>0.316491</v>
       </c>
       <c r="G300" s="5" t="n">
-        <v>-0.7434500000000001</v>
+        <v>-0.386685</v>
       </c>
       <c r="H300" s="5" t="n">
-        <v>-0.474488</v>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.308132</v>
+      </c>
+      <c r="I300" s="5" t="n">
+        <v>-0.114786</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -30140,19 +30164,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Business acquisitions, net of cash acquired 5</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>PurchaseOfBusiness</t>
-        </is>
-      </c>
+          <t>Change in other long term liability 5</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -30163,16 +30183,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G301" s="5" t="n">
-        <v>-15.392198</v>
-      </c>
-      <c r="H301" s="5" t="n">
-        <v>-11.983435</v>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" s="5" t="n">
+        <v>0.427</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -30223,19 +30245,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments to considerations paid for previous business</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Acquisition of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>PurchaseOfPPE</t>
-        </is>
-      </c>
+          <t>Adjustments to considerations paid for previous business combinations</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -30246,16 +30264,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G302" s="5" t="n">
-        <v>-1.303568</v>
-      </c>
-      <c r="H302" s="5" t="n">
-        <v>-1.635186</v>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I302" s="5" t="n">
+        <v>0.463533</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -30306,15 +30326,19 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments to considerations paid for previous business</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Acquisition of intangibles assets</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>Acquisition of property, plant and equipment 8</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -30325,16 +30349,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G303" s="5" t="n">
-        <v>-1.238996</v>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H303" s="5" t="n">
-        <v>-0.770446</v>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.635186</v>
+      </c>
+      <c r="I303" s="5" t="n">
+        <v>-8.062692</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -30385,31 +30409,39 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments to considerations paid for previous business</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Proceeds from sale of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" s="5" t="n">
-        <v>0.105801</v>
-      </c>
-      <c r="F304" s="5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="G304" s="5" t="n">
-        <v>0.416102</v>
+          <t>Acquisition of intangibles assets 11</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H304" s="5" t="n">
-        <v>0.07598199999999999</v>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.770446</v>
+      </c>
+      <c r="I304" s="5" t="n">
+        <v>-0.373835</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -30460,12 +30492,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to considerations paid for previous business</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>(Repayment) increase of secured credit facilities</t>
+          <t>Proceeds from sale of property, plant and equipment</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -30479,16 +30511,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G305" s="5" t="n">
-        <v>6.42337</v>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H305" s="5" t="n">
-        <v>-1.848735</v>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07598199999999999</v>
+      </c>
+      <c r="I305" s="5" t="n">
+        <v>0.903127</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -30539,15 +30571,19 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
+          <t>Adjustments to considerations paid for previous business</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Net cash flows (used in) from financing activities</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -30558,16 +30594,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G306" s="5" t="n">
-        <v>0.317077</v>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H306" s="5" t="n">
-        <v>-8.824703</v>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-14.313085</v>
+      </c>
+      <c r="I306" s="5" t="n">
+        <v>-24.999875</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -30618,19 +30654,15 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Increase (repayment) of secured credit facility</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -30641,16 +30673,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G307" s="5" t="n">
-        <v>2.922898</v>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H307" s="5" t="n">
-        <v>-1.515611</v>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.848735</v>
+      </c>
+      <c r="I307" s="5" t="n">
+        <v>15.868344</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -30701,12 +30733,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Net foreign exchange difference</t>
+          <t>Net cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -30715,21 +30747,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F308" s="5" t="n">
+        <v>-20.954677</v>
       </c>
       <c r="G308" s="5" t="n">
-        <v>0.24694</v>
+        <v>0.317077</v>
       </c>
       <c r="H308" s="5" t="n">
-        <v>-0.053359</v>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.824703</v>
+      </c>
+      <c r="I308" s="5" t="n">
+        <v>8.084624</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -30780,19 +30808,15 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Loss (gain) on disposal of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -30804,10 +30828,10 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>0.364079</v>
+        <v>-0.00674</v>
       </c>
       <c r="H309" s="5" t="n">
-        <v>3.533917</v>
+        <v>0.026766</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -30863,17 +30887,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Cash, ending of period</t>
+          <t>Deferred income tax recovery 15</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>DeferredTax</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -30881,16 +30905,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F310" s="5" t="n">
+        <v>-1.58568</v>
       </c>
       <c r="G310" s="5" t="n">
-        <v>3.533917</v>
+        <v>-0.7434500000000001</v>
       </c>
       <c r="H310" s="5" t="n">
-        <v>1.964947</v>
+        <v>-0.474488</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -30946,30 +30968,34 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>(Gain) loss on disposal of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>Business acquisitions, net of cash acquired 5</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F311" s="5" t="n">
-        <v>0.005617</v>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>-0.00674</v>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-15.392198</v>
+      </c>
+      <c r="H311" s="5" t="n">
+        <v>-11.983435</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -31025,30 +31051,34 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Gain on valuation of derivative financial instruments 14</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>Acquisition of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F312" s="5" t="n">
-        <v>-0.407363</v>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>-0.547562</v>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.303568</v>
+      </c>
+      <c r="H312" s="5" t="n">
+        <v>-1.635186</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -31109,10 +31139,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Business acquisitions, net of acquired cash 5</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>Acquisition of intangibles assets</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -31124,12 +31158,10 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>-15.392198</v>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.238996</v>
+      </c>
+      <c r="H313" s="5" t="n">
+        <v>-0.770446</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -31190,27 +31222,21 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Acquisition of intangibles assets 10</t>
+          <t>Proceeds from sale of property, plant and equipment</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E314" s="5" t="n">
+        <v>0.105801</v>
+      </c>
+      <c r="F314" s="5" t="n">
+        <v>0.008</v>
       </c>
       <c r="G314" s="5" t="n">
-        <v>-1.238996</v>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.416102</v>
+      </c>
+      <c r="H314" s="5" t="n">
+        <v>0.07598199999999999</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -31271,7 +31297,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Increase (repayment) of secured credit facilities</t>
+          <t>(Repayment) increase of secured credit facilities</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -31280,16 +31306,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F315" s="5" t="n">
-        <v>-15.423371</v>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G315" s="5" t="n">
         <v>6.42337</v>
       </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H315" s="5" t="n">
+        <v>-1.848735</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -31345,12 +31371,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Financing cost incurred 14</t>
+          <t>Net cash flows (used in) from financing activities</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -31359,16 +31385,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F316" s="5" t="n">
-        <v>-0.19228</v>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>-0.343136</v>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.317077</v>
+      </c>
+      <c r="H316" s="5" t="n">
+        <v>-8.824703</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -31424,30 +31450,34 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>flows</t>
+          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Amortization of property, plant and equipment 7</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" s="5" t="n">
-        <v>3.574848</v>
-      </c>
-      <c r="F317" s="5" t="n">
-        <v>3.567177</v>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="n">
+        <v>2.922898</v>
+      </c>
+      <c r="H317" s="5" t="n">
+        <v>-1.515611</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -31503,34 +31533,30 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>flows</t>
+          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets 9</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E318" s="5" t="n">
-        <v>6.1639</v>
-      </c>
-      <c r="F318" s="5" t="n">
-        <v>6.1639</v>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net foreign exchange difference</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G318" s="5" t="n">
+        <v>0.24694</v>
+      </c>
+      <c r="H318" s="5" t="n">
+        <v>-0.053359</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -31586,30 +31612,34 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>flows</t>
+          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Amortization of deferred financing costs 13</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" s="5" t="n">
-        <v>0.227435</v>
-      </c>
-      <c r="F319" s="5" t="n">
-        <v>0.43833</v>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G319" s="5" t="n">
+        <v>0.364079</v>
+      </c>
+      <c r="H319" s="5" t="n">
+        <v>3.533917</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
@@ -31665,30 +31695,34 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>flows</t>
+          <t>Financing cost incurred                                                      ‒‒        (343,136)</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Loss (gain) on disposal of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
-      <c r="E320" s="5" t="n">
-        <v>-0.058231</v>
-      </c>
-      <c r="F320" s="5" t="n">
-        <v>0.005617</v>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, ending of period</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="n">
+        <v>3.533917</v>
+      </c>
+      <c r="H320" s="5" t="n">
+        <v>1.964947</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
@@ -31744,25 +31778,25 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>flows</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Gain on valuation of derivative financial instruments 13</t>
+          <t>Gain on valuation of derivative financial instruments 14</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" s="5" t="n">
-        <v>-0.296229</v>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F321" s="5" t="n">
         <v>-0.407363</v>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G321" s="5" t="n">
+        <v>-0.547562</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -31823,25 +31857,27 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>flows</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 14</t>
+          <t>Business acquisitions, net of acquired cash 5</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" s="5" t="n">
-        <v>-0.824051</v>
-      </c>
-      <c r="F322" s="5" t="n">
-        <v>-1.58568</v>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="n">
+        <v>-15.392198</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -31902,25 +31938,31 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>flows</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Change in employees benefits</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr"/>
-      <c r="E323" s="5" t="n">
-        <v>-1.8158</v>
-      </c>
-      <c r="F323" s="5" t="n">
-        <v>0.420364</v>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Acquisition of intangibles assets 10</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="n">
+        <v>-1.238996</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -31981,25 +32023,25 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>flows</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>flows total</t>
+          <t>Increase (repayment) of secured credit facilities</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
-      <c r="E324" s="5" t="n">
-        <v>18.50292</v>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F324" s="5" t="n">
-        <v>19.649687</v>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-15.423371</v>
+      </c>
+      <c r="G324" s="5" t="n">
+        <v>6.42337</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -32060,25 +32102,25 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Variation in provisions</t>
+          <t>Financing cost incurred 14</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
-      <c r="E325" s="5" t="n">
-        <v>-0.015035</v>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F325" s="5" t="n">
-        <v>-0.073875</v>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.19228</v>
+      </c>
+      <c r="G325" s="5" t="n">
+        <v>-0.343136</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -32139,20 +32181,20 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>flows</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Variation in income tax receivable and payable</t>
+          <t>Amortization of property, plant and equipment 7</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" s="5" t="n">
-        <v>0.902316</v>
+        <v>3.574848</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>0.316491</v>
+        <v>3.567177</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -32218,20 +32260,24 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>flows</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Repayment of secured credit facilities</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>Amortization of intangible assets 9</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E327" s="5" t="n">
-        <v>-12</v>
+        <v>6.1639</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>-15.423371</v>
+        <v>6.1639</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
@@ -32297,24 +32343,20 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>flows</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Dividends paid 17</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>CashDividendsPaid</t>
-        </is>
-      </c>
+          <t>Amortization of deferred financing costs 13</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" s="5" t="n">
-        <v>-3.764913</v>
+        <v>0.227435</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-4.771683</v>
+        <v>0.43833</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -32380,22 +32422,20 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>flows</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Purchase of share capital for cancellation 15</t>
+          <t>Loss (gain) on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E329" s="5" t="n">
+        <v>-0.058231</v>
       </c>
       <c r="F329" s="5" t="n">
-        <v>-0.567343</v>
+        <v>0.005617</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -32461,22 +32501,20 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>flows</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Financing cost incurred 13</t>
+          <t>Gain on valuation of derivative financial instruments 13</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E330" s="5" t="n">
+        <v>-0.296229</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>-0.19228</v>
+        <v>-0.407363</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
@@ -32542,24 +32580,24 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>flows</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Net cash flows used in financing activities</t>
+          <t>Deferred income tax recovery 14</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>DeferredTax</t>
         </is>
       </c>
       <c r="E331" s="5" t="n">
-        <v>-15.764913</v>
+        <v>-0.824051</v>
       </c>
       <c r="F331" s="5" t="n">
-        <v>-20.954677</v>
+        <v>-1.58568</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
@@ -32620,33 +32658,25 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>and number of common shares]                             Notes</t>
+          <t>flows</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in employees benefits</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" s="5" t="n">
+        <v>-1.8158</v>
+      </c>
+      <c r="F332" s="5" t="n">
+        <v>0.420364</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -32688,46 +32718,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O332" s="5" t="n">
-        <v>302.187</v>
-      </c>
-      <c r="P332" s="5" t="n">
-        <v>281.035</v>
-      </c>
-      <c r="Q332" s="5" t="n">
-        <v>274.78</v>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>and number of common shares]                             Notes</t>
+          <t>flows</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Operating expenses 7, 11, 21</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>flows total</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" s="5" t="n">
+        <v>18.50292</v>
+      </c>
+      <c r="F333" s="5" t="n">
+        <v>19.649687</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -32774,43 +32802,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P333" s="5" t="n">
-        <v>201.588</v>
-      </c>
-      <c r="Q333" s="5" t="n">
-        <v>203.409</v>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>and number of common shares]                             Notes</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 11, 21</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Variation in provisions</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" s="5" t="n">
+        <v>-0.015035</v>
+      </c>
+      <c r="F334" s="5" t="n">
+        <v>-0.073875</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -32857,39 +32881,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P334" s="5" t="n">
-        <v>39.158</v>
-      </c>
-      <c r="Q334" s="5" t="n">
-        <v>41.762</v>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and other items</t>
+          <t>Variation in income tax receivable and payable</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E335" s="5" t="n">
+        <v>0.902316</v>
+      </c>
+      <c r="F335" s="5" t="n">
+        <v>0.316491</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -32906,61 +32930,69 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J335" s="5" t="n">
-        <v>24.084922</v>
-      </c>
-      <c r="K335" s="5" t="n">
-        <v>25.348087</v>
-      </c>
-      <c r="L335" s="5" t="n">
-        <v>31.85278</v>
-      </c>
-      <c r="M335" s="5" t="n">
-        <v>38.877309</v>
-      </c>
-      <c r="N335" s="5" t="n">
-        <v>55.755566</v>
-      </c>
-      <c r="O335" s="5" t="n">
-        <v>49.796</v>
-      </c>
-      <c r="P335" s="5" t="n">
-        <v>40.289</v>
-      </c>
-      <c r="Q335" s="5" t="n">
-        <v>29.609</v>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment 9</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Repayment of secured credit facilities</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" s="5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F336" s="5" t="n">
+        <v>-15.423371</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -33002,46 +33034,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O336" s="5" t="n">
-        <v>6.712</v>
-      </c>
-      <c r="P336" s="5" t="n">
-        <v>6.744</v>
-      </c>
-      <c r="Q336" s="5" t="n">
-        <v>5.629</v>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Depreciation of right-of-use assets 10</t>
+          <t>Dividends paid 17</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="n">
+        <v>-3.764913</v>
+      </c>
+      <c r="F337" s="5" t="n">
+        <v>-4.771683</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -33083,46 +33117,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O337" s="5" t="n">
-        <v>5.462</v>
-      </c>
-      <c r="P337" s="5" t="n">
-        <v>5.995</v>
-      </c>
-      <c r="Q337" s="5" t="n">
-        <v>6.172</v>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets 12</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Purchase of share capital for cancellation 15</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F338" s="5" t="n">
+        <v>-0.567343</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -33164,30 +33198,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O338" s="5" t="n">
-        <v>6.663</v>
-      </c>
-      <c r="P338" s="5" t="n">
-        <v>6.917</v>
-      </c>
-      <c r="Q338" s="5" t="n">
-        <v>6.903</v>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Asset impairment 20</t>
+          <t>Financing cost incurred 13</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -33196,10 +33236,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F339" s="5" t="n">
+        <v>-0.19228</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -33246,39 +33284,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P339" s="5" t="n">
-        <v>23.412</v>
-      </c>
-      <c r="Q339" s="5" t="n">
-        <v>0.821</v>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Restructuring expenses 15</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash flows used in financing activities</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="n">
+        <v>-15.764913</v>
+      </c>
+      <c r="F340" s="5" t="n">
+        <v>-20.954677</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -33320,14 +33362,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O340" s="5" t="n">
-        <v>2.272</v>
-      </c>
-      <c r="P340" s="5" t="n">
-        <v>1.297</v>
-      </c>
-      <c r="Q340" s="5" t="n">
-        <v>0.289</v>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="341">
@@ -33338,15 +33386,19 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>and number of common shares]                             Notes</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>(Gain) loss on disposal of property, plant and equipment and right-of-use assets</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -33397,16 +33449,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O341" s="5" t="n">
+        <v>302.187</v>
       </c>
       <c r="P341" s="5" t="n">
-        <v>0.014</v>
+        <v>281.035</v>
       </c>
       <c r="Q341" s="5" t="n">
-        <v>-0.207</v>
+        <v>274.78</v>
       </c>
     </row>
     <row r="342">
@@ -33417,15 +33467,19 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>and number of common shares]                             Notes</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Operating earnings (loss)</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>Operating expenses 7, 11, 21</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -33482,10 +33536,10 @@
         </is>
       </c>
       <c r="P342" s="5" t="n">
-        <v>-4.09</v>
+        <v>201.588</v>
       </c>
       <c r="Q342" s="5" t="n">
-        <v>10.002</v>
+        <v>203.409</v>
       </c>
     </row>
     <row r="343">
@@ -33496,15 +33550,19 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>and number of common shares]                             Notes</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>(Gain) on sale and leaseback</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>Selling, general and administrative expenses 11, 21</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -33560,13 +33618,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P343" s="5" t="n">
+        <v>39.158</v>
       </c>
       <c r="Q343" s="5" t="n">
-        <v>-6.1</v>
+        <v>41.762</v>
       </c>
     </row>
     <row r="344">
@@ -33582,7 +33638,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Net financing charges 16</t>
+          <t>Operating earnings before depreciation, amortization and other items</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -33611,39 +33667,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J344" s="5" t="n">
+        <v>24.084922</v>
+      </c>
+      <c r="K344" s="5" t="n">
+        <v>25.348087</v>
+      </c>
+      <c r="L344" s="5" t="n">
+        <v>31.85278</v>
+      </c>
+      <c r="M344" s="5" t="n">
+        <v>38.877309</v>
+      </c>
+      <c r="N344" s="5" t="n">
+        <v>55.755566</v>
       </c>
       <c r="O344" s="5" t="n">
-        <v>5.606</v>
+        <v>49.796</v>
       </c>
       <c r="P344" s="5" t="n">
-        <v>4.856</v>
+        <v>40.289</v>
       </c>
       <c r="Q344" s="5" t="n">
-        <v>4.737</v>
+        <v>29.609</v>
       </c>
     </row>
     <row r="345">
@@ -33659,12 +33705,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Earnings (loss) before income taxes</t>
+          <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -33692,11 +33738,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J345" s="5" t="n">
-        <v>-0.718601</v>
-      </c>
-      <c r="K345" s="5" t="n">
-        <v>10.145333</v>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -33713,16 +33763,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O345" s="5" t="n">
+        <v>6.712</v>
       </c>
       <c r="P345" s="5" t="n">
-        <v>-8.946</v>
+        <v>6.744</v>
       </c>
       <c r="Q345" s="5" t="n">
-        <v>11.365</v>
+        <v>5.629</v>
       </c>
     </row>
     <row r="346">
@@ -33738,10 +33786,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Income tax (recovery) expense 18</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr"/>
+          <t>Depreciation of right-of-use assets 10</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -33792,16 +33844,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O346" s="5" t="n">
+        <v>5.462</v>
       </c>
       <c r="P346" s="5" t="n">
-        <v>2.797</v>
+        <v>5.995</v>
       </c>
       <c r="Q346" s="5" t="n">
-        <v>-0.657</v>
+        <v>6.172</v>
       </c>
     </row>
     <row r="347">
@@ -33817,10 +33867,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Net earnings (loss)</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr"/>
+          <t>Amortization of intangible assets 12</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -33846,11 +33900,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J347" s="5" t="n">
-        <v>-4.79311</v>
-      </c>
-      <c r="K347" s="5" t="n">
-        <v>7.087901</v>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -33867,16 +33925,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O347" s="5" t="n">
+        <v>6.663</v>
       </c>
       <c r="P347" s="5" t="n">
-        <v>-11.743</v>
+        <v>6.917</v>
       </c>
       <c r="Q347" s="5" t="n">
-        <v>12.022</v>
+        <v>6.903</v>
       </c>
     </row>
     <row r="348">
@@ -33892,7 +33948,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Basic and diluted net earnings (loss) per share</t>
+          <t>Asset impairment 20</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -33921,11 +33977,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J348" s="5" t="n">
-        <v>-1.691e-07</v>
-      </c>
-      <c r="K348" s="5" t="n">
-        <v>2.514e-07</v>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -33948,10 +34008,10 @@
         </is>
       </c>
       <c r="P348" s="5" t="n">
-        <v>-4.699999999999999e-07</v>
+        <v>23.412</v>
       </c>
       <c r="Q348" s="5" t="n">
-        <v>4.9e-07</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="349">
@@ -33967,14 +34027,10 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Restructuring expenses 15</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -34000,29 +34056,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J349" s="5" t="n">
-        <v>28.345948</v>
-      </c>
-      <c r="K349" s="5" t="n">
-        <v>28.198474</v>
-      </c>
-      <c r="L349" s="5" t="n">
-        <v>28.060808</v>
-      </c>
-      <c r="M349" s="5" t="n">
-        <v>27.194848</v>
-      </c>
-      <c r="N349" s="5" t="n">
-        <v>26.152557</v>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O349" s="5" t="n">
-        <v>25.898269</v>
+        <v>2.272</v>
       </c>
       <c r="P349" s="5" t="n">
-        <v>24.935338</v>
+        <v>1.297</v>
       </c>
       <c r="Q349" s="5" t="n">
-        <v>24.531225</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="350">
@@ -34033,19 +34099,15 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>and number of common shares]                             Notes</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Operating expenses 7, 11, 21, 23</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>(Gain) loss on disposal of property, plant and equipment and right-of-use assets</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -34096,16 +34158,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O350" s="5" t="n">
-        <v>214.147</v>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P350" s="5" t="n">
-        <v>201.588</v>
-      </c>
-      <c r="Q350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014</v>
+      </c>
+      <c r="Q350" s="5" t="n">
+        <v>-0.207</v>
       </c>
     </row>
     <row r="351">
@@ -34116,19 +34178,15 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>and number of common shares]                             Notes</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 11, 21, 23</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Operating earnings (loss)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -34179,16 +34237,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O351" s="5" t="n">
-        <v>38.244</v>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P351" s="5" t="n">
-        <v>39.158</v>
-      </c>
-      <c r="Q351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.09</v>
+      </c>
+      <c r="Q351" s="5" t="n">
+        <v>10.002</v>
       </c>
     </row>
     <row r="352">
@@ -34204,7 +34262,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Loss (gain) on disposal of property, plant and equipment and right-of-use assets</t>
+          <t>(Gain) on sale and leaseback</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -34258,16 +34316,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O352" s="5" t="n">
-        <v>-0.255</v>
-      </c>
-      <c r="P352" s="5" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="Q352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q352" s="5" t="n">
+        <v>-6.1</v>
       </c>
     </row>
     <row r="353">
@@ -34283,7 +34343,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Operating (loss) earnings</t>
+          <t>Net financing charges 16</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -34338,15 +34398,13 @@
         </is>
       </c>
       <c r="O353" s="5" t="n">
-        <v>28.942</v>
+        <v>5.606</v>
       </c>
       <c r="P353" s="5" t="n">
-        <v>-4.09</v>
-      </c>
-      <c r="Q353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.856</v>
+      </c>
+      <c r="Q353" s="5" t="n">
+        <v>4.737</v>
       </c>
     </row>
     <row r="354">
@@ -34362,7 +34420,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>(Loss) earnings before income taxes</t>
+          <t>Earnings (loss) before income taxes</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -34395,15 +34453,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J354" s="5" t="n">
+        <v>-0.718601</v>
+      </c>
+      <c r="K354" s="5" t="n">
+        <v>10.145333</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -34420,16 +34474,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O354" s="5" t="n">
-        <v>23.336</v>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P354" s="5" t="n">
         <v>-8.946</v>
       </c>
-      <c r="Q354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q354" s="5" t="n">
+        <v>11.365</v>
       </c>
     </row>
     <row r="355">
@@ -34445,7 +34499,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Income tax expense 18</t>
+          <t>Income tax (recovery) expense 18</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -34503,16 +34557,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O355" s="5" t="n">
-        <v>6.002</v>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P355" s="5" t="n">
         <v>2.797</v>
       </c>
-      <c r="Q355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q355" s="5" t="n">
+        <v>-0.657</v>
       </c>
     </row>
     <row r="356">
@@ -34528,10 +34582,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Net (loss) earnings</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>Net earnings (loss)</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -34557,15 +34615,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J356" s="5" t="n">
+        <v>-4.79311</v>
+      </c>
+      <c r="K356" s="5" t="n">
+        <v>7.087901</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -34582,16 +34636,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O356" s="5" t="n">
-        <v>17.334</v>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P356" s="5" t="n">
         <v>-11.743</v>
       </c>
-      <c r="Q356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q356" s="5" t="n">
+        <v>12.022</v>
       </c>
     </row>
     <row r="357">
@@ -34607,7 +34661,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Basic and diluted net (loss) earnings per share</t>
+          <t>Basic and diluted net earnings (loss) per share</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -34636,15 +34690,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J357" s="5" t="n">
+        <v>-1.691e-07</v>
+      </c>
+      <c r="K357" s="5" t="n">
+        <v>2.514e-07</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -34661,16 +34711,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O357" s="5" t="n">
-        <v>6.7e-07</v>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P357" s="5" t="n">
         <v>-4.699999999999999e-07</v>
       </c>
-      <c r="Q357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q357" s="5" t="n">
+        <v>4.9e-07</v>
       </c>
     </row>
     <row r="358">
@@ -34681,61 +34731,67 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E358" s="5" t="n">
-        <v>128.966408</v>
-      </c>
-      <c r="F358" s="5" t="n">
-        <v>131.888065</v>
-      </c>
-      <c r="G358" s="5" t="n">
-        <v>142.298458</v>
-      </c>
-      <c r="H358" s="5" t="n">
-        <v>160.570353</v>
-      </c>
-      <c r="I358" s="5" t="n">
-        <v>179.072759</v>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J358" s="5" t="n">
-        <v>195.08728</v>
+        <v>28.345948</v>
       </c>
       <c r="K358" s="5" t="n">
-        <v>191.669152</v>
+        <v>28.198474</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>204.604433</v>
+        <v>28.060808</v>
       </c>
       <c r="M358" s="5" t="n">
-        <v>226.429947</v>
+        <v>27.194848</v>
       </c>
       <c r="N358" s="5" t="n">
-        <v>272.467276</v>
+        <v>26.152557</v>
       </c>
       <c r="O358" s="5" t="n">
-        <v>302.187383</v>
-      </c>
-      <c r="P358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.898269</v>
+      </c>
+      <c r="P358" s="5" t="n">
+        <v>24.935338</v>
+      </c>
+      <c r="Q358" s="5" t="n">
+        <v>24.531225</v>
       </c>
     </row>
     <row r="359">
@@ -34746,12 +34802,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>and number of common shares]                             Notes</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Operating expenses 7, 10, 19, 21</t>
+          <t>Operating expenses 7, 11, 21, 23</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -34804,16 +34860,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N359" s="5" t="n">
-        <v>181.733453</v>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O359" s="5" t="n">
-        <v>214.146636</v>
-      </c>
-      <c r="P359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>214.147</v>
+      </c>
+      <c r="P359" s="5" t="n">
+        <v>201.588</v>
       </c>
       <c r="Q359" t="inlineStr">
         <is>
@@ -34829,12 +34885,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>and number of common shares]                             Notes</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 10, 19, 21</t>
+          <t>Selling, general and administrative expenses 11, 21, 23</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -34887,16 +34943,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N360" s="5" t="n">
-        <v>34.978257</v>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O360" s="5" t="n">
-        <v>38.244302</v>
-      </c>
-      <c r="P360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>38.244</v>
+      </c>
+      <c r="P360" s="5" t="n">
+        <v>39.158</v>
       </c>
       <c r="Q360" t="inlineStr">
         <is>
@@ -34917,14 +34973,10 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment 8</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Loss (gain) on disposal of property, plant and equipment and right-of-use assets</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -34950,11 +35002,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J361" s="5" t="n">
-        <v>4.295024</v>
-      </c>
-      <c r="K361" s="5" t="n">
-        <v>4.837189</v>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -34966,16 +35022,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N361" s="5" t="n">
-        <v>5.798521</v>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O361" s="5" t="n">
-        <v>6.71226</v>
-      </c>
-      <c r="P361" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.255</v>
+      </c>
+      <c r="P361" s="5" t="n">
+        <v>0.014</v>
       </c>
       <c r="Q361" t="inlineStr">
         <is>
@@ -34996,14 +35052,10 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Depreciation of right-of-use assets 9</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Operating (loss) earnings</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -35049,16 +35101,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N362" s="5" t="n">
-        <v>4.529462</v>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O362" s="5" t="n">
-        <v>5.462662</v>
-      </c>
-      <c r="P362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.942</v>
+      </c>
+      <c r="P362" s="5" t="n">
+        <v>-4.09</v>
       </c>
       <c r="Q362" t="inlineStr">
         <is>
@@ -35079,12 +35131,12 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets 11</t>
+          <t>(Loss) earnings before income taxes</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -35132,16 +35184,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N363" s="5" t="n">
-        <v>3.761866</v>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O363" s="5" t="n">
-        <v>6.663847</v>
-      </c>
-      <c r="P363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>23.336</v>
+      </c>
+      <c r="P363" s="5" t="n">
+        <v>-8.946</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -35162,10 +35214,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Restructuring expenses 14</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr"/>
+          <t>Income tax expense 18</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -35211,16 +35267,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N364" s="5" t="n">
-        <v>1.40974</v>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O364" s="5" t="n">
-        <v>2.271623</v>
-      </c>
-      <c r="P364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.002</v>
+      </c>
+      <c r="P364" s="5" t="n">
+        <v>2.797</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -35241,7 +35297,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Gain on disposal of property, plant and equipment and right-of-use assets</t>
+          <t>Net (loss) earnings</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -35290,16 +35346,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N365" s="5" t="n">
-        <v>-0.408277</v>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O365" s="5" t="n">
-        <v>-0.255033</v>
-      </c>
-      <c r="P365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17.334</v>
+      </c>
+      <c r="P365" s="5" t="n">
+        <v>-11.743</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -35320,14 +35376,10 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Operating earnings</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Basic and diluted net (loss) earnings per share</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -35353,28 +35405,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J366" s="5" t="n">
-        <v>1.123034</v>
-      </c>
-      <c r="K366" s="5" t="n">
-        <v>13.580191</v>
-      </c>
-      <c r="L366" s="5" t="n">
-        <v>13.357785</v>
-      </c>
-      <c r="M366" s="5" t="n">
-        <v>23.279368</v>
-      </c>
-      <c r="N366" s="5" t="n">
-        <v>40.664254</v>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O366" s="5" t="n">
-        <v>28.941086</v>
-      </c>
-      <c r="P366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.7e-07</v>
+      </c>
+      <c r="P366" s="5" t="n">
+        <v>-4.699999999999999e-07</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -35390,65 +35450,51 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Net financing charges 15</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr"/>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="n">
+        <v>128.966408</v>
+      </c>
+      <c r="F367" s="5" t="n">
+        <v>131.888065</v>
+      </c>
+      <c r="G367" s="5" t="n">
+        <v>142.298458</v>
+      </c>
+      <c r="H367" s="5" t="n">
+        <v>160.570353</v>
+      </c>
+      <c r="I367" s="5" t="n">
+        <v>179.072759</v>
+      </c>
+      <c r="J367" s="5" t="n">
+        <v>195.08728</v>
+      </c>
+      <c r="K367" s="5" t="n">
+        <v>191.669152</v>
+      </c>
+      <c r="L367" s="5" t="n">
+        <v>204.604433</v>
+      </c>
+      <c r="M367" s="5" t="n">
+        <v>226.429947</v>
       </c>
       <c r="N367" s="5" t="n">
-        <v>2.571577</v>
+        <v>272.467276</v>
       </c>
       <c r="O367" s="5" t="n">
-        <v>5.605644</v>
+        <v>302.187383</v>
       </c>
       <c r="P367" t="inlineStr">
         <is>
@@ -35469,17 +35515,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Earnings before income taxes</t>
+          <t>Operating expenses 7, 10, 19, 21</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -35517,17 +35563,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L368" s="5" t="n">
-        <v>10.284299</v>
-      </c>
-      <c r="M368" s="5" t="n">
-        <v>21.053154</v>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N368" s="5" t="n">
-        <v>38.092677</v>
+        <v>181.733453</v>
       </c>
       <c r="O368" s="5" t="n">
-        <v>23.335442</v>
+        <v>214.146636</v>
       </c>
       <c r="P368" t="inlineStr">
         <is>
@@ -35548,17 +35598,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Income tax expense 17</t>
+          <t>Selling, general and administrative expenses 10, 19, 21</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -35607,10 +35657,10 @@
         </is>
       </c>
       <c r="N369" s="5" t="n">
-        <v>9.656539</v>
+        <v>34.978257</v>
       </c>
       <c r="O369" s="5" t="n">
-        <v>6.001754</v>
+        <v>38.244302</v>
       </c>
       <c r="P369" t="inlineStr">
         <is>
@@ -35636,12 +35686,12 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Net earnings</t>
+          <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -35669,27 +35719,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L370" s="5" t="n">
-        <v>7.494693</v>
-      </c>
-      <c r="M370" s="5" t="n">
-        <v>15.752288</v>
+      <c r="J370" s="5" t="n">
+        <v>4.295024</v>
+      </c>
+      <c r="K370" s="5" t="n">
+        <v>4.837189</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N370" s="5" t="n">
-        <v>28.436138</v>
+        <v>5.798521</v>
       </c>
       <c r="O370" s="5" t="n">
-        <v>17.333688</v>
+        <v>6.71226</v>
       </c>
       <c r="P370" t="inlineStr">
         <is>
@@ -35715,10 +35765,14 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Basic and diluted net earnings per share</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr"/>
+          <t>Depreciation of right-of-use assets 9</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -35754,17 +35808,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L371" s="5" t="n">
-        <v>2.671e-07</v>
-      </c>
-      <c r="M371" s="5" t="n">
-        <v>5.792e-07</v>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N371" s="5" t="n">
-        <v>1.09e-06</v>
+        <v>4.529462</v>
       </c>
       <c r="O371" s="5" t="n">
-        <v>6.7e-07</v>
+        <v>5.462662</v>
       </c>
       <c r="P371" t="inlineStr">
         <is>
@@ -35785,17 +35843,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Operating expenses 6, 9, 18, 20</t>
+          <t>Amortization of intangible assets 11</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -35838,16 +35896,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M372" s="5" t="n">
-        <v>158.259751</v>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N372" s="5" t="n">
-        <v>181.733453</v>
-      </c>
-      <c r="O372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.761866</v>
+      </c>
+      <c r="O372" s="5" t="n">
+        <v>6.663847</v>
       </c>
       <c r="P372" t="inlineStr">
         <is>
@@ -35868,19 +35926,15 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 9, 18, 20</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Restructuring expenses 14</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -35921,16 +35975,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M373" s="5" t="n">
-        <v>29.292887</v>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N373" s="5" t="n">
-        <v>34.978257</v>
-      </c>
-      <c r="O373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.40974</v>
+      </c>
+      <c r="O373" s="5" t="n">
+        <v>2.271623</v>
       </c>
       <c r="P373" t="inlineStr">
         <is>
@@ -35956,14 +36010,10 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment 7</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Gain on disposal of property, plant and equipment and right-of-use assets</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -35999,19 +36049,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L374" s="5" t="n">
-        <v>5.443472</v>
-      </c>
-      <c r="M374" s="5" t="n">
-        <v>5.313542</v>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N374" s="5" t="n">
-        <v>5.798521</v>
-      </c>
-      <c r="O374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.408277</v>
+      </c>
+      <c r="O374" s="5" t="n">
+        <v>-0.255033</v>
       </c>
       <c r="P374" t="inlineStr">
         <is>
@@ -36037,12 +36089,12 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Depreciation of right-of-use assets 8</t>
+          <t>Operating earnings</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -36070,29 +36122,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J375" s="5" t="n">
+        <v>1.123034</v>
+      </c>
+      <c r="K375" s="5" t="n">
+        <v>13.580191</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>5.089028</v>
+        <v>13.357785</v>
       </c>
       <c r="M375" s="5" t="n">
-        <v>4.829664</v>
+        <v>23.279368</v>
       </c>
       <c r="N375" s="5" t="n">
-        <v>4.529462</v>
-      </c>
-      <c r="O375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>40.664254</v>
+      </c>
+      <c r="O375" s="5" t="n">
+        <v>28.941086</v>
       </c>
       <c r="P375" t="inlineStr">
         <is>
@@ -36118,14 +36164,10 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets 10</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Net financing charges 15</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -36151,25 +36193,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J376" s="5" t="n">
-        <v>2.088659</v>
-      </c>
-      <c r="K376" s="5" t="n">
-        <v>2.193257</v>
-      </c>
-      <c r="L376" s="5" t="n">
-        <v>3.355591</v>
-      </c>
-      <c r="M376" s="5" t="n">
-        <v>3.381104</v>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N376" s="5" t="n">
-        <v>3.761866</v>
-      </c>
-      <c r="O376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.571577</v>
+      </c>
+      <c r="O376" s="5" t="n">
+        <v>5.605644</v>
       </c>
       <c r="P376" t="inlineStr">
         <is>
@@ -36195,10 +36243,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Asset impairment 13</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>Earnings before income taxes</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -36234,23 +36286,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L377" s="5" t="n">
+        <v>10.284299</v>
       </c>
       <c r="M377" s="5" t="n">
-        <v>2.073631</v>
-      </c>
-      <c r="N377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.053154</v>
+      </c>
+      <c r="N377" s="5" t="n">
+        <v>38.092677</v>
+      </c>
+      <c r="O377" s="5" t="n">
+        <v>23.335442</v>
       </c>
       <c r="P377" t="inlineStr">
         <is>
@@ -36276,10 +36322,14 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Restructuring expenses 13</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
+          <t>Income tax expense 17</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -36326,12 +36376,10 @@
         </is>
       </c>
       <c r="N378" s="5" t="n">
-        <v>1.40974</v>
-      </c>
-      <c r="O378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.656539</v>
+      </c>
+      <c r="O378" s="5" t="n">
+        <v>6.001754</v>
       </c>
       <c r="P378" t="inlineStr">
         <is>
@@ -36357,10 +36405,14 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Net financing charges 14</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>Net earnings</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -36397,18 +36449,16 @@
         </is>
       </c>
       <c r="L379" s="5" t="n">
-        <v>3.073486</v>
+        <v>7.494693</v>
       </c>
       <c r="M379" s="5" t="n">
-        <v>2.226214</v>
+        <v>15.752288</v>
       </c>
       <c r="N379" s="5" t="n">
-        <v>2.571577</v>
-      </c>
-      <c r="O379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.436138</v>
+      </c>
+      <c r="O379" s="5" t="n">
+        <v>17.333688</v>
       </c>
       <c r="P379" t="inlineStr">
         <is>
@@ -36434,14 +36484,10 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Income tax expense 16</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Basic and diluted net earnings per share</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -36478,18 +36524,16 @@
         </is>
       </c>
       <c r="L380" s="5" t="n">
-        <v>2.789606</v>
+        <v>2.671e-07</v>
       </c>
       <c r="M380" s="5" t="n">
-        <v>5.300866</v>
+        <v>5.792e-07</v>
       </c>
       <c r="N380" s="5" t="n">
-        <v>9.656539</v>
-      </c>
-      <c r="O380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.09e-06</v>
+      </c>
+      <c r="O380" s="5" t="n">
+        <v>6.7e-07</v>
       </c>
       <c r="P380" t="inlineStr">
         <is>
@@ -36515,7 +36559,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Operating expenses 6, 9, 19, 21</t>
+          <t>Operating expenses 6, 9, 18, 20</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -36558,16 +36602,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L381" s="5" t="n">
-        <v>147.355947</v>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M381" s="5" t="n">
         <v>158.259751</v>
       </c>
-      <c r="N381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N381" s="5" t="n">
+        <v>181.733453</v>
       </c>
       <c r="O381" t="inlineStr">
         <is>
@@ -36598,7 +36642,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 9, 19, 21</t>
+          <t>Selling, general and administrative expenses 9, 18, 20</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -36641,16 +36685,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L382" s="5" t="n">
-        <v>25.395706</v>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M382" s="5" t="n">
         <v>29.292887</v>
       </c>
-      <c r="N382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N382" s="5" t="n">
+        <v>34.978257</v>
       </c>
       <c r="O382" t="inlineStr">
         <is>
@@ -36681,10 +36725,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Asset impairment 18</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>Depreciation of property, plant and equipment 7</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -36721,15 +36769,13 @@
         </is>
       </c>
       <c r="L383" s="5" t="n">
-        <v>2.770479</v>
+        <v>5.443472</v>
       </c>
       <c r="M383" s="5" t="n">
-        <v>2.073631</v>
-      </c>
-      <c r="N383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.313542</v>
+      </c>
+      <c r="N383" s="5" t="n">
+        <v>5.798521</v>
       </c>
       <c r="O383" t="inlineStr">
         <is>
@@ -36760,10 +36806,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Restructuring expense 13</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>Depreciation of right-of-use assets 8</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -36800,17 +36850,13 @@
         </is>
       </c>
       <c r="L384" s="5" t="n">
-        <v>1.836425</v>
-      </c>
-      <c r="M384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.089028</v>
+      </c>
+      <c r="M384" s="5" t="n">
+        <v>4.829664</v>
+      </c>
+      <c r="N384" s="5" t="n">
+        <v>4.529462</v>
       </c>
       <c r="O384" t="inlineStr">
         <is>
@@ -36836,17 +36882,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Operating expenses 7, 9, 17</t>
+          <t>Amortization of intangible assets 10</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -36854,14 +36900,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F385" s="5" t="n">
-        <v>88.723062</v>
-      </c>
-      <c r="G385" s="5" t="n">
-        <v>93.89313199999999</v>
-      </c>
-      <c r="H385" s="5" t="n">
-        <v>114.447567</v>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
@@ -36869,25 +36921,19 @@
         </is>
       </c>
       <c r="J385" s="5" t="n">
-        <v>146.294758</v>
+        <v>2.088659</v>
       </c>
       <c r="K385" s="5" t="n">
-        <v>143.765907</v>
-      </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.193257</v>
+      </c>
+      <c r="L385" s="5" t="n">
+        <v>3.355591</v>
+      </c>
+      <c r="M385" s="5" t="n">
+        <v>3.381104</v>
+      </c>
+      <c r="N385" s="5" t="n">
+        <v>3.761866</v>
       </c>
       <c r="O385" t="inlineStr">
         <is>
@@ -36913,19 +36959,15 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 9, 17</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Asset impairment 13</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -36936,32 +36978,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G386" s="5" t="n">
-        <v>15.315871</v>
-      </c>
-      <c r="H386" s="5" t="n">
-        <v>18.740282</v>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J386" s="5" t="n">
-        <v>24.7076</v>
-      </c>
-      <c r="K386" s="5" t="n">
-        <v>22.555158</v>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M386" s="5" t="n">
+        <v>2.073631</v>
       </c>
       <c r="N386" t="inlineStr">
         <is>
@@ -36997,14 +37045,10 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Depreciation of right-of-use assets 4</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Restructuring expenses 13</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -37035,8 +37079,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K387" s="5" t="n">
-        <v>4.696686</v>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -37048,10 +37094,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N387" s="5" t="n">
+        <v>1.40974</v>
       </c>
       <c r="O387" t="inlineStr">
         <is>
@@ -37082,7 +37126,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Loss (gain) on disposal of property, plant and equipment and right- of-use assets</t>
+          <t>Net financing charges 14</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -37111,26 +37155,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J388" s="5" t="n">
-        <v>-0.77774</v>
-      </c>
-      <c r="K388" s="5" t="n">
-        <v>0.164991</v>
-      </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L388" s="5" t="n">
+        <v>3.073486</v>
+      </c>
+      <c r="M388" s="5" t="n">
+        <v>2.226214</v>
+      </c>
+      <c r="N388" s="5" t="n">
+        <v>2.571577</v>
       </c>
       <c r="O388" t="inlineStr">
         <is>
@@ -37161,10 +37203,14 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Goodwill impairment 11</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>Income tax expense 16</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -37190,28 +37236,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J389" s="5" t="n">
-        <v>16.137</v>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L389" s="5" t="n">
+        <v>2.789606</v>
+      </c>
+      <c r="M389" s="5" t="n">
+        <v>5.300866</v>
+      </c>
+      <c r="N389" s="5" t="n">
+        <v>9.656539</v>
       </c>
       <c r="O389" t="inlineStr">
         <is>
@@ -37237,15 +37279,19 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Restructuring (recovery) expenses 13</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>Operating expenses 6, 9, 19, 21</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -37271,21 +37317,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J390" s="5" t="n">
-        <v>1.218945</v>
-      </c>
-      <c r="K390" s="5" t="n">
-        <v>-0.124227</v>
-      </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L390" s="5" t="n">
+        <v>147.355947</v>
+      </c>
+      <c r="M390" s="5" t="n">
+        <v>158.259751</v>
       </c>
       <c r="N390" t="inlineStr">
         <is>
@@ -37316,15 +37362,19 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Operating earnings before depreciation, amortization and</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Financing charges, net 14</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr"/>
+          <t>Selling, general and administrative expenses 9, 19, 21</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -37350,21 +37400,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J391" s="5" t="n">
-        <v>1.841635</v>
-      </c>
-      <c r="K391" s="5" t="n">
-        <v>3.434858</v>
-      </c>
-      <c r="L391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L391" s="5" t="n">
+        <v>25.395706</v>
+      </c>
+      <c r="M391" s="5" t="n">
+        <v>29.292887</v>
       </c>
       <c r="N391" t="inlineStr">
         <is>
@@ -37400,14 +37450,10 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Income tax expense 15</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Asset impairment 18</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -37433,21 +37479,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J392" s="5" t="n">
-        <v>4.074509</v>
-      </c>
-      <c r="K392" s="5" t="n">
-        <v>3.057432</v>
-      </c>
-      <c r="L392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L392" s="5" t="n">
+        <v>2.770479</v>
+      </c>
+      <c r="M392" s="5" t="n">
+        <v>2.073631</v>
       </c>
       <c r="N392" t="inlineStr">
         <is>
@@ -37478,19 +37524,15 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Operating expenses 7, 9, 18</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Restructuring expense 13</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -37506,11 +37548,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H393" s="5" t="n">
-        <v>114.447567</v>
-      </c>
-      <c r="I393" s="5" t="n">
-        <v>130.325375</v>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
@@ -37522,10 +37568,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L393" s="5" t="n">
+        <v>1.836425</v>
       </c>
       <c r="M393" t="inlineStr">
         <is>
@@ -37566,12 +37610,12 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 9, 18</t>
+          <t>Operating expenses 7, 9, 17</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -37579,31 +37623,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F394" s="5" t="n">
+        <v>88.723062</v>
+      </c>
+      <c r="G394" s="5" t="n">
+        <v>93.89313199999999</v>
       </c>
       <c r="H394" s="5" t="n">
-        <v>18.740282</v>
-      </c>
-      <c r="I394" s="5" t="n">
-        <v>22.920182</v>
-      </c>
-      <c r="J394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>114.447567</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J394" s="5" t="n">
+        <v>146.294758</v>
+      </c>
+      <c r="K394" s="5" t="n">
+        <v>143.765907</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -37644,15 +37682,19 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core operations of Printer Gateway</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr"/>
+          <t>Selling, general and administrative expenses 9, 17</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -37663,26 +37705,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G395" s="5" t="n">
+        <v>15.315871</v>
       </c>
       <c r="H395" s="5" t="n">
-        <v>27.382504</v>
-      </c>
-      <c r="I395" s="5" t="n">
-        <v>25.827202</v>
-      </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.740282</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J395" s="5" t="n">
+        <v>24.7076</v>
+      </c>
+      <c r="K395" s="5" t="n">
+        <v>22.555158</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -37723,15 +37761,19 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Amortization of property, plant and equipment 8</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr"/>
+          <t>Depreciation of right-of-use assets 4</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -37747,21 +37789,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H396" s="5" t="n">
-        <v>4.519575</v>
-      </c>
-      <c r="I396" s="5" t="n">
-        <v>3.713196</v>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K396" s="5" t="n">
+        <v>4.696686</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
@@ -37802,19 +37846,15 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets 11</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Loss (gain) on disposal of property, plant and equipment and right- of-use assets</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -37830,21 +37870,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H397" s="5" t="n">
-        <v>1.916581</v>
-      </c>
-      <c r="I397" s="5" t="n">
-        <v>1.682702</v>
-      </c>
-      <c r="J397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J397" s="5" t="n">
+        <v>-0.77774</v>
+      </c>
+      <c r="K397" s="5" t="n">
+        <v>0.164991</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -37885,12 +37925,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Loss on disposal of property, plant and equipment</t>
+          <t>Goodwill impairment 11</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -37909,16 +37949,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H398" s="5" t="n">
-        <v>0.026766</v>
-      </c>
-      <c r="I398" s="5" t="n">
-        <v>0.114533</v>
-      </c>
-      <c r="J398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J398" s="5" t="n">
+        <v>16.137</v>
       </c>
       <c r="K398" t="inlineStr">
         <is>
@@ -37964,12 +38006,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Shutdown of non-core operations of Printer Gateway 8, 10, 11, 12</t>
+          <t>Restructuring (recovery) expenses 13</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -37993,18 +38035,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I399" s="5" t="n">
-        <v>2.191765</v>
-      </c>
-      <c r="J399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J399" s="5" t="n">
+        <v>1.218945</v>
+      </c>
+      <c r="K399" s="5" t="n">
+        <v>-0.124227</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
@@ -38045,19 +38085,15 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Operating earnings</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Financing charges, net 14</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -38073,21 +38109,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H400" s="5" t="n">
-        <v>20.919582</v>
-      </c>
-      <c r="I400" s="5" t="n">
-        <v>18.125006</v>
-      </c>
-      <c r="J400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J400" s="5" t="n">
+        <v>1.841635</v>
+      </c>
+      <c r="K400" s="5" t="n">
+        <v>3.434858</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -38128,15 +38164,19 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core</t>
+          <t>Operating earnings before depreciation, amortization and</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Financing charges, net 15</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr"/>
+          <t>Income tax expense 15</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -38152,21 +38192,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H401" s="5" t="n">
-        <v>0.852029</v>
-      </c>
-      <c r="I401" s="5" t="n">
-        <v>1.078191</v>
-      </c>
-      <c r="J401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J401" s="5" t="n">
+        <v>4.074509</v>
+      </c>
+      <c r="K401" s="5" t="n">
+        <v>3.057432</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
@@ -38207,17 +38247,17 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Earnings before income taxes</t>
+          <t>Operating expenses 7, 9, 18</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -38236,10 +38276,10 @@
         </is>
       </c>
       <c r="H402" s="5" t="n">
-        <v>20.067553</v>
+        <v>114.447567</v>
       </c>
       <c r="I402" s="5" t="n">
-        <v>17.046815</v>
+        <v>130.325375</v>
       </c>
       <c r="J402" t="inlineStr">
         <is>
@@ -38290,17 +38330,17 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>property, plant and equipment and shutdown of non-core</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Income tax expense 16</t>
+          <t>Selling, general and administrative expenses 9, 18</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -38319,10 +38359,10 @@
         </is>
       </c>
       <c r="H403" s="5" t="n">
-        <v>5.474809</v>
+        <v>18.740282</v>
       </c>
       <c r="I403" s="5" t="n">
-        <v>4.655987</v>
+        <v>22.920182</v>
       </c>
       <c r="J403" t="inlineStr">
         <is>
@@ -38378,14 +38418,10 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Net earnings</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>property, plant and equipment and shutdown of non-core operations of Printer Gateway</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -38402,10 +38438,10 @@
         </is>
       </c>
       <c r="H404" s="5" t="n">
-        <v>14.592744</v>
+        <v>27.382504</v>
       </c>
       <c r="I404" s="5" t="n">
-        <v>12.390828</v>
+        <v>25.827202</v>
       </c>
       <c r="J404" t="inlineStr">
         <is>
@@ -38461,7 +38497,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Basic and diluted net earnings per share</t>
+          <t>Amortization of property, plant and equipment 8</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -38481,10 +38517,10 @@
         </is>
       </c>
       <c r="H405" s="5" t="n">
-        <v>5.093999999999999e-07</v>
+        <v>4.519575</v>
       </c>
       <c r="I405" s="5" t="n">
-        <v>4.348e-07</v>
+        <v>3.713196</v>
       </c>
       <c r="J405" t="inlineStr">
         <is>
@@ -38540,12 +38576,12 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Amortization of intangible assets 11</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -38564,10 +38600,10 @@
         </is>
       </c>
       <c r="H406" s="5" t="n">
-        <v>28.645053</v>
+        <v>1.916581</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>28.495406</v>
+        <v>1.682702</v>
       </c>
       <c r="J406" t="inlineStr">
         <is>
@@ -38618,12 +38654,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization and loss</t>
+          <t>property, plant and equipment and shutdown of non-core</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>(gain) on disposal of property, plant and equipment</t>
+          <t>Loss on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -38637,16 +38673,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G407" s="5" t="n">
-        <v>33.089455</v>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H407" s="5" t="n">
-        <v>27.382504</v>
-      </c>
-      <c r="I407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.026766</v>
+      </c>
+      <c r="I407" s="5" t="n">
+        <v>0.114533</v>
       </c>
       <c r="J407" t="inlineStr">
         <is>
@@ -38697,12 +38733,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization and loss</t>
+          <t>property, plant and equipment and shutdown of non-core</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Amortization of property, plant and equipment 8</t>
+          <t>Shutdown of non-core operations of Printer Gateway 8, 10, 11, 12</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
@@ -38716,16 +38752,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G408" s="5" t="n">
-        <v>4.110569</v>
-      </c>
-      <c r="H408" s="5" t="n">
-        <v>4.519575</v>
-      </c>
-      <c r="I408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I408" s="5" t="n">
+        <v>2.191765</v>
       </c>
       <c r="J408" t="inlineStr">
         <is>
@@ -38776,17 +38814,17 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization and loss</t>
+          <t>property, plant and equipment and shutdown of non-core</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets 10</t>
+          <t>Operating earnings</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -38799,16 +38837,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G409" s="5" t="n">
-        <v>6.211107</v>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H409" s="5" t="n">
-        <v>1.916581</v>
-      </c>
-      <c r="I409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20.919582</v>
+      </c>
+      <c r="I409" s="5" t="n">
+        <v>18.125006</v>
       </c>
       <c r="J409" t="inlineStr">
         <is>
@@ -38859,12 +38897,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization and loss</t>
+          <t>property, plant and equipment and shutdown of non-core</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Loss (gain) on disposal of property, plant and equipment</t>
+          <t>Financing charges, net 15</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -38878,16 +38916,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G410" s="5" t="n">
-        <v>-0.00674</v>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H410" s="5" t="n">
-        <v>0.026766</v>
-      </c>
-      <c r="I410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.852029</v>
+      </c>
+      <c r="I410" s="5" t="n">
+        <v>1.078191</v>
       </c>
       <c r="J410" t="inlineStr">
         <is>
@@ -38938,17 +38976,17 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization and loss</t>
+          <t>property, plant and equipment and shutdown of non-core</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Operating earnings</t>
+          <t>Earnings before income taxes</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -38961,16 +38999,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G411" s="5" t="n">
-        <v>22.774519</v>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H411" s="5" t="n">
-        <v>20.919582</v>
-      </c>
-      <c r="I411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20.067553</v>
+      </c>
+      <c r="I411" s="5" t="n">
+        <v>17.046815</v>
       </c>
       <c r="J411" t="inlineStr">
         <is>
@@ -39021,15 +39059,19 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization and loss</t>
+          <t>property, plant and equipment and shutdown of non-core</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Financing charges, net 14</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>Income tax expense 16</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -39040,16 +39082,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G412" s="5" t="n">
-        <v>0.966419</v>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H412" s="5" t="n">
-        <v>0.852029</v>
-      </c>
-      <c r="I412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.474809</v>
+      </c>
+      <c r="I412" s="5" t="n">
+        <v>4.655987</v>
       </c>
       <c r="J412" t="inlineStr">
         <is>
@@ -39100,17 +39142,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization and loss</t>
+          <t>property, plant and equipment and shutdown of non-core</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Earnings before income taxes</t>
+          <t>Net earnings</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -39123,16 +39165,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G413" s="5" t="n">
-        <v>21.8081</v>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H413" s="5" t="n">
-        <v>20.067553</v>
-      </c>
-      <c r="I413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.592744</v>
+      </c>
+      <c r="I413" s="5" t="n">
+        <v>12.390828</v>
       </c>
       <c r="J413" t="inlineStr">
         <is>
@@ -39183,19 +39225,15 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization and loss</t>
+          <t>property, plant and equipment and shutdown of non-core</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Income tax expense 15</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Basic and diluted net earnings per share</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -39206,16 +39244,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G414" s="5" t="n">
-        <v>5.8773</v>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H414" s="5" t="n">
-        <v>5.474809</v>
-      </c>
-      <c r="I414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.093999999999999e-07</v>
+      </c>
+      <c r="I414" s="5" t="n">
+        <v>4.348e-07</v>
       </c>
       <c r="J414" t="inlineStr">
         <is>
@@ -39266,17 +39304,17 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization and loss</t>
+          <t>property, plant and equipment and shutdown of non-core</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Net earnings</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -39289,16 +39327,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G415" s="5" t="n">
-        <v>15.9308</v>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H415" s="5" t="n">
-        <v>14.592744</v>
-      </c>
-      <c r="I415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.645053</v>
+      </c>
+      <c r="I415" s="5" t="n">
+        <v>28.495406</v>
       </c>
       <c r="J415" t="inlineStr">
         <is>
@@ -39354,7 +39392,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Basic and diluted net earnings per share</t>
+          <t>(gain) on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -39369,10 +39407,10 @@
         </is>
       </c>
       <c r="G416" s="5" t="n">
-        <v>5.541e-07</v>
+        <v>33.089455</v>
       </c>
       <c r="H416" s="5" t="n">
-        <v>5.093999999999999e-07</v>
+        <v>27.382504</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
@@ -39433,14 +39471,10 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Amortization of property, plant and equipment 8</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -39452,10 +39486,10 @@
         </is>
       </c>
       <c r="G417" s="5" t="n">
-        <v>28.751008</v>
+        <v>4.110569</v>
       </c>
       <c r="H417" s="5" t="n">
-        <v>28.645053</v>
+        <v>4.519575</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -39511,17 +39545,17 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating earnings before amortization and loss</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 9,17</t>
+          <t>Amortization of intangible assets 10</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -39529,16 +39563,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F418" s="5" t="n">
-        <v>16.945995</v>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G418" s="5" t="n">
-        <v>15.315871</v>
-      </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.211107</v>
+      </c>
+      <c r="H418" s="5" t="n">
+        <v>1.916581</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -39594,12 +39628,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on</t>
+          <t>Operating earnings before amortization and loss</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on disposal of property, plant and equipment</t>
+          <t>Loss (gain) on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -39608,16 +39642,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F419" s="5" t="n">
-        <v>26.219008</v>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G419" s="5" t="n">
-        <v>33.089455</v>
-      </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00674</v>
+      </c>
+      <c r="H419" s="5" t="n">
+        <v>0.026766</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -39673,30 +39707,34 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on</t>
+          <t>Operating earnings before amortization and loss</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Amortization of property, plant and equipment 8</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr"/>
+          <t>Operating earnings</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F420" s="5" t="n">
-        <v>3.567177</v>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G420" s="5" t="n">
-        <v>4.110569</v>
-      </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>22.774519</v>
+      </c>
+      <c r="H420" s="5" t="n">
+        <v>20.919582</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -39752,34 +39790,30 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on</t>
+          <t>Operating earnings before amortization and loss</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets 10</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Financing charges, net 14</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F421" s="5" t="n">
-        <v>6.1639</v>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G421" s="5" t="n">
-        <v>6.211107</v>
-      </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.966419</v>
+      </c>
+      <c r="H421" s="5" t="n">
+        <v>0.852029</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -39835,30 +39869,34 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on</t>
+          <t>Operating earnings before amortization and loss</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>(Gain) loss on disposal of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>Earnings before income taxes</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F422" s="5" t="n">
-        <v>0.005617</v>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G422" s="5" t="n">
-        <v>-0.00674</v>
-      </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.8081</v>
+      </c>
+      <c r="H422" s="5" t="n">
+        <v>20.067553</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -39914,17 +39952,17 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on</t>
+          <t>Operating earnings before amortization and loss</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Operating earnings</t>
+          <t>Income tax expense 15</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -39932,16 +39970,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F423" s="5" t="n">
-        <v>16.482314</v>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G423" s="5" t="n">
-        <v>22.774519</v>
-      </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.8773</v>
+      </c>
+      <c r="H423" s="5" t="n">
+        <v>5.474809</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -39997,30 +40035,34 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on</t>
+          <t>Operating earnings before amortization and loss</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Financing charges, net 14</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>Net earnings</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F424" s="5" t="n">
-        <v>1.333699</v>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G424" s="5" t="n">
-        <v>0.966419</v>
-      </c>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.9308</v>
+      </c>
+      <c r="H424" s="5" t="n">
+        <v>14.592744</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -40076,34 +40118,30 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on</t>
+          <t>Operating earnings before amortization and loss</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Earnings before income taxes</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Basic and diluted net earnings per share</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F425" s="5" t="n">
-        <v>15.148615</v>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G425" s="5" t="n">
-        <v>21.8081</v>
-      </c>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.541e-07</v>
+      </c>
+      <c r="H425" s="5" t="n">
+        <v>5.093999999999999e-07</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -40159,17 +40197,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on</t>
+          <t>Operating earnings before amortization and loss</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Income tax expense 15</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -40177,16 +40215,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F426" s="5" t="n">
-        <v>4.101273</v>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G426" s="5" t="n">
-        <v>5.8773</v>
-      </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.751008</v>
+      </c>
+      <c r="H426" s="5" t="n">
+        <v>28.645053</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -40242,17 +40280,17 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, (gain) loss on</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Net earnings</t>
+          <t>Selling, general and administrative expenses 9,17</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -40261,10 +40299,10 @@
         </is>
       </c>
       <c r="F427" s="5" t="n">
-        <v>11.047342</v>
+        <v>16.945995</v>
       </c>
       <c r="G427" s="5" t="n">
-        <v>15.9308</v>
+        <v>15.315871</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
@@ -40330,7 +40368,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Basic and diluted net earnings per share</t>
+          <t>Operating earnings before amortization, (gain) loss on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -40340,10 +40378,10 @@
         </is>
       </c>
       <c r="F428" s="5" t="n">
-        <v>3.822e-07</v>
+        <v>26.219008</v>
       </c>
       <c r="G428" s="5" t="n">
-        <v>5.541e-07</v>
+        <v>33.089455</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
@@ -40409,24 +40447,20 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Amortization of property, plant and equipment 8</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F429" s="5" t="n">
-        <v>28.905181</v>
+        <v>3.567177</v>
       </c>
       <c r="G429" s="5" t="n">
-        <v>28.751008</v>
+        <v>4.110569</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
@@ -40487,29 +40521,29 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating earnings before amortization, (gain) loss on</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Operating expenses 6, 16</t>
+          <t>Amortization of intangible assets 10</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E430" s="5" t="n">
-        <v>85.259978</v>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F430" s="5" t="n">
-        <v>88.723062</v>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.1639</v>
+      </c>
+      <c r="G430" s="5" t="n">
+        <v>6.211107</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
@@ -40570,29 +40604,25 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating earnings before amortization, (gain) loss on</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 16</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E431" s="5" t="n">
-        <v>15.72793</v>
+          <t>(Gain) loss on disposal of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F431" s="5" t="n">
-        <v>16.945995</v>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005617</v>
+      </c>
+      <c r="G431" s="5" t="n">
+        <v>-0.00674</v>
       </c>
       <c r="H431" t="inlineStr">
         <is>
@@ -40653,25 +40683,29 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on</t>
+          <t>Operating earnings before amortization, (gain) loss on</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on disposal of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr"/>
-      <c r="E432" s="5" t="n">
-        <v>27.9785</v>
+          <t>Operating earnings</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F432" s="5" t="n">
-        <v>26.219008</v>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16.482314</v>
+      </c>
+      <c r="G432" s="5" t="n">
+        <v>22.774519</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -40732,25 +40766,25 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on</t>
+          <t>Operating earnings before amortization, (gain) loss on</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Amortization of property, plant and equipment 7</t>
+          <t>Financing charges, net 14</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
-      <c r="E433" s="5" t="n">
-        <v>3.574848</v>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F433" s="5" t="n">
-        <v>3.567177</v>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.333699</v>
+      </c>
+      <c r="G433" s="5" t="n">
+        <v>0.966419</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
@@ -40811,29 +40845,29 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on</t>
+          <t>Operating earnings before amortization, (gain) loss on</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets 9</t>
+          <t>Earnings before income taxes</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E434" s="5" t="n">
-        <v>6.1639</v>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F434" s="5" t="n">
-        <v>6.1639</v>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.148615</v>
+      </c>
+      <c r="G434" s="5" t="n">
+        <v>21.8081</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
@@ -40894,25 +40928,29 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on</t>
+          <t>Operating earnings before amortization, (gain) loss on</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Loss (gain) on disposal of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr"/>
-      <c r="E435" s="5" t="n">
-        <v>-0.058231</v>
+          <t>Income tax expense 15</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F435" s="5" t="n">
-        <v>0.005617</v>
-      </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.101273</v>
+      </c>
+      <c r="G435" s="5" t="n">
+        <v>5.8773</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
@@ -40973,29 +41011,29 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on</t>
+          <t>Operating earnings before amortization, (gain) loss on</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Operating earnings</t>
+          <t>Net earnings</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E436" s="5" t="n">
-        <v>18.297983</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F436" s="5" t="n">
-        <v>16.482314</v>
-      </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.047342</v>
+      </c>
+      <c r="G436" s="5" t="n">
+        <v>15.9308</v>
       </c>
       <c r="H436" t="inlineStr">
         <is>
@@ -41056,25 +41094,25 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on</t>
+          <t>Operating earnings before amortization, (gain) loss on</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Financing charges 13</t>
+          <t>Basic and diluted net earnings per share</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
-      <c r="E437" s="5" t="n">
-        <v>2.853971</v>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F437" s="5" t="n">
-        <v>1.333699</v>
-      </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.822e-07</v>
+      </c>
+      <c r="G437" s="5" t="n">
+        <v>5.541e-07</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
@@ -41135,29 +41173,29 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on</t>
+          <t>Operating earnings before amortization, (gain) loss on</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Earnings before income taxes</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E438" s="5" t="n">
-        <v>15.444012</v>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F438" s="5" t="n">
-        <v>15.148615</v>
-      </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.905181</v>
+      </c>
+      <c r="G438" s="5" t="n">
+        <v>28.751008</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
@@ -41218,24 +41256,24 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Income tax expense 14</t>
+          <t>Operating expenses 6, 16</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E439" s="5" t="n">
-        <v>3.912964</v>
+        <v>85.259978</v>
       </c>
       <c r="F439" s="5" t="n">
-        <v>4.101273</v>
+        <v>88.723062</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
@@ -41301,24 +41339,24 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Operating earnings before amortization, loss (gain) on</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Net earnings</t>
+          <t>Selling, general and administrative expenses 16</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E440" s="5" t="n">
-        <v>11.531048</v>
+        <v>15.72793</v>
       </c>
       <c r="F440" s="5" t="n">
-        <v>11.047342</v>
+        <v>16.945995</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
@@ -41389,15 +41427,15 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Basic and diluted net earnings per share</t>
+          <t>Operating earnings before amortization, loss (gain) on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
       <c r="E441" s="5" t="n">
-        <v>3.982e-07</v>
+        <v>27.9785</v>
       </c>
       <c r="F441" s="5" t="n">
-        <v>3.822e-07</v>
+        <v>26.219008</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
@@ -41468,71 +41506,802 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
+          <t>Amortization of property, plant and equipment 7</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" s="5" t="n">
+        <v>3.574848</v>
+      </c>
+      <c r="F442" s="5" t="n">
+        <v>3.567177</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Operating earnings before amortization, loss (gain) on</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Amortization of intangible assets 9</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E443" s="5" t="n">
+        <v>6.1639</v>
+      </c>
+      <c r="F443" s="5" t="n">
+        <v>6.1639</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Operating earnings before amortization, loss (gain) on</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Loss (gain) on disposal of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" s="5" t="n">
+        <v>-0.058231</v>
+      </c>
+      <c r="F444" s="5" t="n">
+        <v>0.005617</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Operating earnings before amortization, loss (gain) on</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Operating earnings</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E445" s="5" t="n">
+        <v>18.297983</v>
+      </c>
+      <c r="F445" s="5" t="n">
+        <v>16.482314</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Operating earnings before amortization, loss (gain) on</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Financing charges 13</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" s="5" t="n">
+        <v>2.853971</v>
+      </c>
+      <c r="F446" s="5" t="n">
+        <v>1.333699</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Operating earnings before amortization, loss (gain) on</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Earnings before income taxes</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E447" s="5" t="n">
+        <v>15.444012</v>
+      </c>
+      <c r="F447" s="5" t="n">
+        <v>15.148615</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Operating earnings before amortization, loss (gain) on</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Income tax expense 14</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E448" s="5" t="n">
+        <v>3.912964</v>
+      </c>
+      <c r="F448" s="5" t="n">
+        <v>4.101273</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Operating earnings before amortization, loss (gain) on</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Net earnings</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E449" s="5" t="n">
+        <v>11.531048</v>
+      </c>
+      <c r="F449" s="5" t="n">
+        <v>11.047342</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Operating earnings before amortization, loss (gain) on</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Basic and diluted net earnings per share</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" s="5" t="n">
+        <v>3.982e-07</v>
+      </c>
+      <c r="F450" s="5" t="n">
+        <v>3.822e-07</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Operating earnings before amortization, loss (gain) on</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
           <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr">
+      <c r="D451" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E442" s="5" t="n">
+      <c r="E451" s="5" t="n">
         <v>28.960867</v>
       </c>
-      <c r="F442" s="5" t="n">
+      <c r="F451" s="5" t="n">
         <v>28.905181</v>
       </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q442" t="inlineStr">
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
         <is>
           <t>-</t>
         </is>
